--- a/data/dividends_info_20260924.xlsx
+++ b/data/dividends_info_20260924.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>45.2599983215332</v>
+        <v>44.88000106811523</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1988510900080634</v>
+        <v>0.2005347545856901</v>
       </c>
       <c r="J2" t="n">
         <v>172</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.84999847412109</v>
+        <v>63.84999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.079414057780341</v>
+        <v>1.096319525025072</v>
       </c>
       <c r="J3" t="n">
         <v>151</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.779999732971191</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6833713191890466</v>
+        <v>0.6818181670401711</v>
       </c>
       <c r="J4" t="n">
         <v>81</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5249999761581421</v>
+        <v>0.5149999856948853</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7619047965051923</v>
+        <v>0.7766990507005224</v>
       </c>
       <c r="J5" t="n">
         <v>81</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45.2599983215332</v>
+        <v>44.88000106811523</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1988510900080634</v>
+        <v>0.2005347545856901</v>
       </c>
       <c r="J6" t="n">
         <v>81</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.085000038146973</v>
+        <v>2.075000047683716</v>
       </c>
       <c r="I7" t="n">
-        <v>3.693045495981532</v>
+        <v>3.710843288218411</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>24.17499923706055</v>
+        <v>24.375</v>
       </c>
       <c r="I8" t="n">
-        <v>1.116856291710185</v>
+        <v>1.107692307692308</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.93000030517578</v>
+        <v>24.88999938964844</v>
       </c>
       <c r="I9" t="n">
-        <v>2.366626525381584</v>
+        <v>2.370429949650286</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.949999809265137</v>
+        <v>5.889999866485596</v>
       </c>
       <c r="I10" t="n">
-        <v>3.36134464556733</v>
+        <v>3.395585815510971</v>
       </c>
       <c r="J10" t="n">
         <v>53</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.78999996185303</v>
+        <v>10.76000022888184</v>
       </c>
       <c r="I11" t="n">
-        <v>4.263206687917371</v>
+        <v>4.27509284586514</v>
       </c>
       <c r="J11" t="n">
         <v>32</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8.100000381469727</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7407407058555365</v>
+        <v>0.7317073340929389</v>
       </c>
       <c r="J12" t="n">
         <v>25</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.5249999761581421</v>
+        <v>0.5149999856948853</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7619047965051923</v>
+        <v>0.7766990507005224</v>
       </c>
       <c r="J13" t="n">
         <v>25</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7.699999809265137</v>
+        <v>7.420000076293945</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4935065057310254</v>
+        <v>0.5121293747880902</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>24.17499923706055</v>
+        <v>24.375</v>
       </c>
       <c r="I16" t="n">
-        <v>1.116856291710185</v>
+        <v>1.107692307692308</v>
       </c>
       <c r="J16" t="n">
         <v>-3</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.922999978065491</v>
+        <v>1.927000045776367</v>
       </c>
       <c r="I17" t="n">
-        <v>2.964118598552516</v>
+        <v>2.95796567960305</v>
       </c>
       <c r="J17" t="n">
         <v>-3</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>45.2599983215332</v>
+        <v>44.88000106811523</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1988510900080634</v>
+        <v>0.2005347545856901</v>
       </c>
       <c r="J18" t="n">
         <v>-3</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>95.44999694824219</v>
+        <v>94.69999694824219</v>
       </c>
       <c r="I19" t="n">
-        <v>1.393399730249539</v>
+        <v>1.404435103336809</v>
       </c>
       <c r="J19" t="n">
         <v>-3</v>
@@ -2724,7 +2724,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2758,7 +2758,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2809,7 +2809,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2843,7 +2843,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2860,7 +2860,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2877,7 +2877,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2911,7 +2911,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2921,14 +2921,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2945,7 +2945,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2962,7 +2962,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2996,7 +2996,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3006,14 +3006,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3047,7 +3047,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3064,7 +3064,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3081,7 +3081,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3098,7 +3098,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3108,14 +3108,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3132,7 +3132,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3149,7 +3149,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3166,7 +3166,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3234,7 +3234,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3268,7 +3268,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3285,7 +3285,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3302,7 +3302,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3319,7 +3319,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3353,7 +3353,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3370,7 +3370,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3387,7 +3387,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3404,7 +3404,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3438,7 +3438,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3455,7 +3455,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3482,14 +3482,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3506,7 +3506,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3523,7 +3523,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3533,14 +3533,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3557,7 +3557,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3608,7 +3608,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3642,7 +3642,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3669,14 +3669,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3693,7 +3693,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3703,14 +3703,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3727,7 +3727,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3761,7 +3761,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3880,7 +3880,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3897,7 +3897,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3914,7 +3914,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3948,7 +3948,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3965,7 +3965,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3982,7 +3982,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3999,7 +3999,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4016,7 +4016,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4033,7 +4033,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4050,7 +4050,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4084,7 +4084,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4101,7 +4101,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Dipietro Group S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4135,7 +4135,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4152,7 +4152,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4162,14 +4162,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4186,7 +4186,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4220,7 +4220,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4237,7 +4237,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4254,7 +4254,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4271,7 +4271,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4288,7 +4288,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4298,14 +4298,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4407,7 +4407,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4424,7 +4424,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4441,7 +4441,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4458,7 +4458,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4475,7 +4475,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4492,7 +4492,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4502,14 +4502,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4526,7 +4526,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4543,7 +4543,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4560,7 +4560,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4577,7 +4577,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4594,7 +4594,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4611,7 +4611,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4628,7 +4628,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4645,7 +4645,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4662,7 +4662,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4696,7 +4696,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4713,7 +4713,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Dipietro Group S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4730,7 +4730,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4747,7 +4747,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4764,7 +4764,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4781,7 +4781,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4815,7 +4815,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4866,7 +4866,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4883,7 +4883,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4893,14 +4893,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4917,7 +4917,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4934,7 +4934,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>SB Annual Report</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5029,14 +5029,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SB Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5063,14 +5063,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5080,14 +5080,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5165,14 +5165,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5182,14 +5182,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5325,7 +5325,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5335,14 +5335,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5352,14 +5352,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5427,7 +5427,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5478,7 +5478,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5512,7 +5512,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5539,14 +5539,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5563,7 +5563,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5580,7 +5580,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5624,14 +5624,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5665,7 +5665,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5682,7 +5682,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5699,7 +5699,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5716,7 +5716,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5754,78 +5754,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ESI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>OLIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>